--- a/public/Add_Users_Template_Example.xlsx
+++ b/public/Add_Users_Template_Example.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
   <cols>
     <col width="12.796875" customWidth="1" min="1" max="4"/>
@@ -538,6 +538,81 @@
           <t>บทบาท</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ลาป่วย (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ลาคลอดบุตร (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ลากิจส่วนตัว (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ลาพักผ่อน (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ลาอุปสมบท (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ลาตรวจเลือก/เตรียมพล (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ลาไปศึกษา (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ลาช่วยเหลือภริยาที่คลอดบุตร (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ลาฟื้นฟูสมรรถภาพด้านอาชีพ (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ลาถือศีล/ปฏิบัติธรรม สตรี (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ลาองค์การระหว่างประเทศ (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ลาติดตามคู่สมรส (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ลาประกอบพิธีฮัจย์ (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ลาฝึกอบรม/วิจัย/ดูงาน (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ไปราชการ (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1020,7 +1095,19 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="8">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>Lists!$D$1:$D$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>Lists!$A$1:$A$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>Lists!$B$1:$B$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>Lists!$C$1:$C$8</formula1>
+    </dataValidation>
     <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$D$1:$D$3</formula1>
     </dataValidation>
